--- a/astro-site/public/dl/kit-tareas-hotel/09-housekeeping.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/09-housekeeping.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pulir suelos (parqué, mármol, moqueta según material)</t>
+          <t>Pulir suelos duros (parqué, mármol) y lavar la moqueta con inyección-extracción, según material</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
